--- a/uploads/ItemsSample.xlsx
+++ b/uploads/ItemsSample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Git Project\Warehouse\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.abbaspoor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4F94D8-8F16-4DF6-B6BB-0D09BBBE129E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74CE8E1-9BAF-4280-9584-95BD7F7D06EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30630" yWindow="1830" windowWidth="15300" windowHeight="7725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="31">
   <si>
     <t>project_code</t>
   </si>
@@ -78,62 +78,53 @@
     <t>recipient_delivery</t>
   </si>
   <si>
-    <t>کد پروژه</t>
-  </si>
-  <si>
-    <t>محل</t>
-  </si>
-  <si>
-    <t>ردیف</t>
-  </si>
-  <si>
-    <t>تحویل گیرنده اول</t>
-  </si>
-  <si>
-    <t>شرکت</t>
-  </si>
-  <si>
-    <t>واحد</t>
-  </si>
-  <si>
-    <t>کد پرسنلی</t>
-  </si>
-  <si>
-    <t>محل استقرار</t>
-  </si>
-  <si>
-    <t>کد شناسایی سیستم</t>
-  </si>
-  <si>
-    <t>گروه بندی</t>
-  </si>
-  <si>
-    <t>مدل</t>
-  </si>
-  <si>
-    <t>سریال</t>
-  </si>
-  <si>
-    <t>کد اموال</t>
-  </si>
-  <si>
-    <t>تحویل گیرنده دوم</t>
-  </si>
-  <si>
-    <t>توضیحات</t>
-  </si>
-  <si>
-    <t>مختوم شده</t>
-  </si>
-  <si>
-    <t>جزییات اختتام</t>
+    <t>AN392</t>
+  </si>
+  <si>
+    <t>آذر نیک اختر</t>
+  </si>
+  <si>
+    <t>سرپرست آی تی</t>
+  </si>
+  <si>
+    <t>انبار آی تی خرامه (392)</t>
+  </si>
+  <si>
+    <t>فکورصنعت</t>
+  </si>
+  <si>
+    <t>کیس</t>
+  </si>
+  <si>
+    <t>i5</t>
+  </si>
+  <si>
+    <t>AN393</t>
+  </si>
+  <si>
+    <t>AN394</t>
+  </si>
+  <si>
+    <t>AN395</t>
+  </si>
+  <si>
+    <t>AN396</t>
+  </si>
+  <si>
+    <t>AN397</t>
+  </si>
+  <si>
+    <t>AN398</t>
+  </si>
+  <si>
+    <t>AN399</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,14 +141,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="178"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF006100"/>
@@ -165,15 +148,13 @@
       <charset val="178"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,11 +164,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -215,23 +191,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
-    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -525,29 +496,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -600,60 +571,264 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>392</v>
+      </c>
+      <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2">
+        <v>2210</v>
+      </c>
+      <c r="H2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2">
+        <v>638009</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>392</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>2210</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="K3" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="M3">
+        <v>638010</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>392</v>
+      </c>
+      <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4">
+        <v>2210</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4">
+        <v>638011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>392</v>
+      </c>
+      <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5">
+        <v>2210</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5">
+        <v>638012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>392</v>
+      </c>
+      <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6">
+        <v>2210</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6">
+        <v>638013</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>392</v>
+      </c>
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7">
+        <v>2210</v>
+      </c>
+      <c r="H7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7">
+        <v>638014</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>392</v>
+      </c>
+      <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8">
+        <v>2210</v>
+      </c>
+      <c r="H8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8">
+        <v>638015</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>392</v>
+      </c>
+      <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>33</v>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9">
+        <v>2210</v>
+      </c>
+      <c r="H9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9">
+        <v>608016</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="N1">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"محمود شاقاسی رودی"</formula>

--- a/uploads/ItemsSample.xlsx
+++ b/uploads/ItemsSample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.abbaspoor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74CE8E1-9BAF-4280-9584-95BD7F7D06EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D798D1B-A4AF-488D-B953-45E08A321489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="3840" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>project_code</t>
   </si>
@@ -76,48 +76,6 @@
   </si>
   <si>
     <t>recipient_delivery</t>
-  </si>
-  <si>
-    <t>AN392</t>
-  </si>
-  <si>
-    <t>آذر نیک اختر</t>
-  </si>
-  <si>
-    <t>سرپرست آی تی</t>
-  </si>
-  <si>
-    <t>انبار آی تی خرامه (392)</t>
-  </si>
-  <si>
-    <t>فکورصنعت</t>
-  </si>
-  <si>
-    <t>کیس</t>
-  </si>
-  <si>
-    <t>i5</t>
-  </si>
-  <si>
-    <t>AN393</t>
-  </si>
-  <si>
-    <t>AN394</t>
-  </si>
-  <si>
-    <t>AN395</t>
-  </si>
-  <si>
-    <t>AN396</t>
-  </si>
-  <si>
-    <t>AN397</t>
-  </si>
-  <si>
-    <t>AN398</t>
-  </si>
-  <si>
-    <t>AN399</t>
   </si>
 </sst>
 </file>
@@ -496,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -571,262 +529,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>392</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2">
-        <v>2210</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2">
-        <v>638009</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>392</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>2210</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>638010</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>392</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4">
-        <v>2210</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4">
-        <v>638011</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>392</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5">
-        <v>2210</v>
-      </c>
-      <c r="H5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M5">
-        <v>638012</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>392</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6">
-        <v>2210</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6">
-        <v>638013</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>392</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7">
-        <v>2210</v>
-      </c>
-      <c r="H7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7">
-        <v>638014</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>392</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8">
-        <v>2210</v>
-      </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8">
-        <v>638015</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>392</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9">
-        <v>2210</v>
-      </c>
-      <c r="H9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9">
-        <v>608016</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="N1">
